--- a/docs/CrewLogic-Future-Work-Register.xlsx
+++ b/docs/CrewLogic-Future-Work-Register.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -47,11 +47,15 @@
       <color rgb="009C6500"/>
     </font>
     <font>
+      <i val="1"/>
+      <color rgb="00808080"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="001E7A34"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -81,6 +85,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
     <fill>
@@ -115,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -148,6 +157,9 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -531,7 +543,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CrewLogic Future-Work Register - stable IDs FW-01..FW-51 (do NOT renumber) - verified vs code 2026-07-05  |  6 Done, 10 Partial, 35 Open</t>
+          <t>CrewLogic Future-Work Register - stable IDs FW-01..FW-51 (do NOT renumber) - 2026-07-05  |  7 Done, 7 Partial, 2 Dropped, 35 Open</t>
         </is>
       </c>
     </row>
@@ -946,14 +958,14 @@
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr"/>
-      <c r="G12" s="10" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
+          <t>Dropped</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>Desktop drag-to-move across days + voice move work; no date/time reschedule picker on the job popup.</t>
+          <t>KILLED by owner 2026-07-05 — not pursuing (desktop drag-move + voice move already cover this).</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1148,7 @@
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr"/>
-      <c r="G17" s="11" t="inlineStr">
+      <c r="G17" s="12" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -1174,14 +1186,14 @@
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr"/>
-      <c r="G18" s="10" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>Write path fully wired (execute-&gt;method16 move/cancel/duration) but NOT prod-write-verified (dev VONIGO_READONLY); unified popup not mirrored on Manage Jobs voice bar.</t>
+          <t>VERIFIED DONE — owner confirms the dispatcher write path (move/cancel/duration) works in prod, 2026-07-05.</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1376,7 @@
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr"/>
-      <c r="G23" s="11" t="inlineStr">
+      <c r="G23" s="12" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -1478,14 +1490,14 @@
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr"/>
-      <c r="G26" s="10" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="G26" s="11" t="inlineStr">
+        <is>
+          <t>Dropped</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>serviceStates captured/editable + feeds Town Price Lookup; per-estimator default state parked + signup-time capture not started.</t>
+          <t>KILLED by owner 2026-07-05 — native users already enter ZIPs in pricing; redundant.</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1756,7 @@
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr"/>
-      <c r="G33" s="11" t="inlineStr">
+      <c r="G33" s="12" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -1820,7 +1832,7 @@
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr"/>
-      <c r="G35" s="11" t="inlineStr">
+      <c r="G35" s="12" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -1972,7 +1984,7 @@
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr"/>
-      <c r="G39" s="11" t="inlineStr">
+      <c r="G39" s="12" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -2010,7 +2022,7 @@
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr"/>
-      <c r="G40" s="11" t="inlineStr">
+      <c r="G40" s="12" t="inlineStr">
         <is>
           <t>Done</t>
         </is>

--- a/docs/CrewLogic-Future-Work-Register.xlsx
+++ b/docs/CrewLogic-Future-Work-Register.xlsx
@@ -543,7 +543,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CrewLogic Future-Work Register - stable IDs FW-01..FW-51 (do NOT renumber) - 2026-07-05  |  7 Done, 7 Partial, 2 Dropped, 35 Open</t>
+          <t>CrewLogic Future-Work Register - stable IDs FW-01..FW-51 (do NOT renumber) - 2026-07-05  |  8 Done, 6 Partial, 2 Dropped, 35 Open</t>
         </is>
       </c>
     </row>
@@ -2516,14 +2516,14 @@
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr"/>
-      <c r="G53" s="10" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="G53" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>DMARC/SPF/DKIM done; real-signup inbox re-test remains (runtime).</t>
+          <t>VERIFIED DONE — owner tested confirm-email inbox delivery, working 2026-07-05 (DMARC/SPF/DKIM).</t>
         </is>
       </c>
     </row>

--- a/docs/CrewLogic-Future-Work-Register.xlsx
+++ b/docs/CrewLogic-Future-Work-Register.xlsx
@@ -2333,7 +2333,7 @@
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>File is gitignored + never committed (strip effectively covered); keys NOT rotated — rotation remains.</t>
+          <t>Local n8n export REDACTED to MY_* placeholders (Google/Anthropic/Motive keys + Sheet ID) + backup with real keys DELETED 2026-07-05; verified not in repo/history/index. Remaining: rotate ONLY if the original ever synced to cloud/shared (else close).</t>
         </is>
       </c>
     </row>

--- a/docs/CrewLogic-Future-Work-Register.xlsx
+++ b/docs/CrewLogic-Future-Work-Register.xlsx
@@ -543,7 +543,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CrewLogic Future-Work Register - stable IDs FW-01..FW-51 (do NOT renumber) - 2026-07-05  |  8 Done, 6 Partial, 2 Dropped, 35 Open</t>
+          <t>CrewLogic Future-Work Register - stable IDs FW-01..FW-51 (do NOT renumber) - 2026-07-05  |  9 Done, 5 Partial, 2 Dropped, 35 Open</t>
         </is>
       </c>
     </row>
@@ -2326,14 +2326,14 @@
         </is>
       </c>
       <c r="F48" s="8" t="inlineStr"/>
-      <c r="G48" s="10" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="G48" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>Local n8n export REDACTED to MY_* placeholders (Google/Anthropic/Motive keys + Sheet ID) + backup with real keys DELETED 2026-07-05; verified not in repo/history/index. Remaining: rotate ONLY if the original ever synced to cloud/shared (else close).</t>
+          <t>VERIFIED DONE 2026-07-05 — export redacted to MY_* placeholders + real-key backup deleted; verified not in repo/history/index; owner confirms the file never synced/shared → keys never left the machine, no rotation needed.</t>
         </is>
       </c>
     </row>

--- a/docs/CrewLogic-Future-Work-Register.xlsx
+++ b/docs/CrewLogic-Future-Work-Register.xlsx
@@ -44,15 +44,15 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="001E7A34"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="009C6500"/>
     </font>
     <font>
       <i val="1"/>
       <color rgb="00808080"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="001E7A34"/>
     </font>
   </fonts>
   <fills count="9">
@@ -84,17 +84,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D9D9D9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -543,7 +543,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CrewLogic Future-Work Register - stable IDs FW-01..FW-51 (do NOT renumber) - 2026-07-05  |  9 Done, 5 Partial, 2 Dropped, 35 Open</t>
+          <t>CrewLogic Future-Work Register - stable IDs FW-01..FW-51 (do NOT renumber) - 2026-07-05  |  10 Done, 5 Partial, 2 Dropped, 34 Open</t>
         </is>
       </c>
     </row>
@@ -692,14 +692,14 @@
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr"/>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>Not started</t>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>Owner action — per-franchise Vault token doesn't carry dev-&gt;prod; re-enter #90 Motive token in prod Settings.</t>
+          <t>VERIFIED DONE 2026-07-05 — prod #90 Motive already set up: pull token connected (3 trucks, telematics_credentials is_active) + webhook secret configured (motive_webhook_config). Migration 0033 preserved it; re-entry was never actually needed. (Prod validation stamp June 12; re-save on app.crewlogicai.com to refresh — optional.)</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr"/>
-      <c r="G11" s="10" t="inlineStr">
+      <c r="G11" s="11" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr"/>
-      <c r="G12" s="11" t="inlineStr">
+      <c r="G12" s="12" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr"/>
-      <c r="G17" s="12" t="inlineStr">
+      <c r="G17" s="10" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -1186,7 +1186,7 @@
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr"/>
-      <c r="G18" s="12" t="inlineStr">
+      <c r="G18" s="10" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -1338,7 +1338,7 @@
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr"/>
-      <c r="G22" s="10" t="inlineStr">
+      <c r="G22" s="11" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr"/>
-      <c r="G23" s="12" t="inlineStr">
+      <c r="G23" s="10" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -1490,7 +1490,7 @@
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr"/>
-      <c r="G26" s="11" t="inlineStr">
+      <c r="G26" s="12" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
-      <c r="G28" s="10" t="inlineStr">
+      <c r="G28" s="11" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr"/>
-      <c r="G33" s="12" t="inlineStr">
+      <c r="G33" s="10" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -1832,7 +1832,7 @@
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr"/>
-      <c r="G35" s="12" t="inlineStr">
+      <c r="G35" s="10" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -1870,7 +1870,7 @@
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr"/>
-      <c r="G36" s="10" t="inlineStr">
+      <c r="G36" s="11" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -1984,7 +1984,7 @@
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr"/>
-      <c r="G39" s="12" t="inlineStr">
+      <c r="G39" s="10" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -2022,7 +2022,7 @@
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr"/>
-      <c r="G40" s="12" t="inlineStr">
+      <c r="G40" s="10" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr"/>
-      <c r="G45" s="10" t="inlineStr">
+      <c r="G45" s="11" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -2326,7 +2326,7 @@
         </is>
       </c>
       <c r="F48" s="8" t="inlineStr"/>
-      <c r="G48" s="12" t="inlineStr">
+      <c r="G48" s="10" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -2516,7 +2516,7 @@
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr"/>
-      <c r="G53" s="12" t="inlineStr">
+      <c r="G53" s="10" t="inlineStr">
         <is>
           <t>Done</t>
         </is>

--- a/docs/CrewLogic-Future-Work-Register.xlsx
+++ b/docs/CrewLogic-Future-Work-Register.xlsx
@@ -543,7 +543,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CrewLogic Future-Work Register - stable IDs FW-01..FW-51 (do NOT renumber) - 2026-07-05  |  10 Done, 5 Partial, 2 Dropped, 34 Open</t>
+          <t>CrewLogic Future-Work Register - stable IDs FW-01..FW-51 (do NOT renumber) - 2026-07-05  |  10 Done, 5 Partial, 3 Dropped, 33 Open</t>
         </is>
       </c>
     </row>
@@ -1110,14 +1110,14 @@
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr"/>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>Not started</t>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>Dropped</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>crewlogic-weather is state-level; dashboard + Job Plan only; not narrowed to office point, not on trucks screen.</t>
+          <t>KILLED by owner 2026-07-05 — not needed (state-level weather on dashboard + Job Plan is sufficient).</t>
         </is>
       </c>
     </row>

--- a/docs/CrewLogic-Future-Work-Register.xlsx
+++ b/docs/CrewLogic-Future-Work-Register.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -54,8 +54,12 @@
       <i val="1"/>
       <color rgb="00808080"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -97,6 +101,11 @@
         <fgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00BDD7EE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -124,7 +133,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -160,6 +169,9 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -543,7 +555,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CrewLogic Future-Work Register - stable IDs FW-01..FW-51 (do NOT renumber) - 2026-07-05  |  10 Done, 5 Partial, 3 Dropped, 33 Open</t>
+          <t>CrewLogic Future-Work Register - stable IDs FW-01..FW-51 (do NOT renumber) - 2026-07-05  |  10 Done, 2 In progress, 5 Partial, 3 Dropped, 31 Open</t>
         </is>
       </c>
     </row>
@@ -1224,14 +1236,14 @@
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr"/>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>Not started</t>
+      <c r="G19" s="13" t="inlineStr">
+        <is>
+          <t>In progress</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>townFromAddress returns raw UPPERCASE Vonigo segment (job-geofence-sync:123); title-case tweak.</t>
+          <t>BUILT ON DEV v5.50.1 — job-alert town title-cased on display (_titleCaseTown in _geofenceAlertRow); covers existing + new alerts. Pending owner test + prod approval.</t>
         </is>
       </c>
     </row>
@@ -1414,14 +1426,14 @@
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr"/>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>Not started</t>
+      <c r="G24" s="13" t="inlineStr">
+        <is>
+          <t>In progress</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>calcShed still uses ~half-volume formula w/ no joist/shingle inputs (index.html ~23508).</t>
+          <t>BUILT ON DEV v5.50.1 — calcShed rewritten: walls + floor + PITCHED roof debris volume with floor-joist / roof-rafter / shingle-layer inputs + on-screen component breakdown (~1.55x the old structure figure; fixes the missing-roof undercount). Pending owner test/calibration + prod approval.</t>
         </is>
       </c>
     </row>

--- a/docs/CrewLogic-Future-Work-Register.xlsx
+++ b/docs/CrewLogic-Future-Work-Register.xlsx
@@ -1243,7 +1243,7 @@
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>BUILT ON DEV v5.50.1 — job-alert town title-cased on display (_titleCaseTown in _geofenceAlertRow); covers existing + new alerts. Pending owner test + prod approval.</t>
+          <t>BUILT ON DEV v5.50.2 — town/city title-cased on job ALERTS (_geofenceAlertRow) AND the schedule board (job chip + hover/sticky popup City row) via _titleCaseTown. Other surfaces (price-lookup town list, customer list) left as-is unless flagged. Pending owner test + prod approval.</t>
         </is>
       </c>
     </row>

--- a/docs/CrewLogic-Future-Work-Register.xlsx
+++ b/docs/CrewLogic-Future-Work-Register.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -54,12 +54,8 @@
       <i val="1"/>
       <color rgb="00808080"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="001F4E79"/>
-    </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -101,11 +97,6 @@
         <fgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00BDD7EE"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -133,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -169,9 +160,6 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -555,7 +543,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CrewLogic Future-Work Register - stable IDs FW-01..FW-51 (do NOT renumber) - 2026-07-05  |  10 Done, 2 In progress, 5 Partial, 3 Dropped, 31 Open</t>
+          <t>CrewLogic Future-Work Register - stable IDs FW-01..FW-51 (do NOT renumber) - 2026-07-05  |  12 Done, 5 Partial, 3 Dropped, 31 Open</t>
         </is>
       </c>
     </row>
@@ -1236,14 +1224,14 @@
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr"/>
-      <c r="G19" s="13" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>BUILT ON DEV v5.50.2 — town/city title-cased on job ALERTS (_geofenceAlertRow) AND the schedule board (job chip + hover/sticky popup City row) via _titleCaseTown. Other surfaces (price-lookup town list, customer list) left as-is unless flagged. Pending owner test + prod approval.</t>
+          <t>VERIFIED DONE (prod v5.50.2, 2026-07-05) — town/city title-cased on job ALERTS (_geofenceAlertRow) AND the schedule board (job chip + hover/sticky popup City row) via _titleCaseTown. Client names untouched. Other surfaces (price-lookup, customer list) intentionally left as-is.</t>
         </is>
       </c>
     </row>
@@ -1426,14 +1414,14 @@
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr"/>
-      <c r="G24" s="13" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="G24" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>BUILT ON DEV v5.50.1 — calcShed rewritten: walls + floor + PITCHED roof debris volume with floor-joist / roof-rafter / shingle-layer inputs + on-screen component breakdown (~1.55x the old structure figure; fixes the missing-roof undercount). Pending owner test/calibration + prod approval.</t>
+          <t>VERIFIED DONE (prod v5.50.2, 2026-07-05) — calcShed rewritten: walls + floor + PITCHED roof debris volume with floor-joist / roof-rafter / shingle-layer inputs + on-screen walls/floor/roof breakdown (fixes the missing-roof undercount). Owner-tested/approved. Thickness factors remain calibratable if field use shows drift.</t>
         </is>
       </c>
     </row>

--- a/docs/CrewLogic-Future-Work-Register.xlsx
+++ b/docs/CrewLogic-Future-Work-Register.xlsx
@@ -527,7 +527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H53"/>
+  <dimension ref="A1:H54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -543,7 +543,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CrewLogic Future-Work Register - stable IDs FW-01..FW-51 (do NOT renumber) - 2026-07-05  |  12 Done, 5 Partial, 3 Dropped, 31 Open</t>
+          <t>CrewLogic Future-Work Register - stable IDs FW-01..FW-51 (do NOT renumber) - 2026-07-05  |  12 Done, 5 Partial, 3 Dropped, 31 Open  |  +FW-67 added 2026-08-16 (Recycling manual-revenue; note: FW-52..66 allocated outside this file)</t>
         </is>
       </c>
     </row>
@@ -2524,6 +2524,44 @@
       <c r="H53" s="4" t="inlineStr">
         <is>
           <t>VERIFIED DONE — owner tested confirm-email inbox delivery, working 2026-07-05 (DMARC/SPF/DKIM).</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>FW-67</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>Recycling / Revenue</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>Manual recycling-revenue entry (un-geofenced trips)</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>Recycling revenue is captured ONLY for geofence-derived visits (geofence exit dwell -&gt; visit -&gt; settle amount). Trips where the truck never triggered the recycling geofence (device unplugged, GPS gap, facility not geofenced, dwell too short) have NO visit row, so that revenue is uncounted.</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>Backlog (owner 2026-08-16). Add an "Add trip / manual entry" path on the Recycling screen (date, truck/route, facility, amount+weight, no geofence backing, flagged manual). Draft a contract addendum (manual-entry data model + dedupe rule) for sign-off BEFORE code.</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="n"/>
+      <c r="G54" s="10" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>Extends docs/contract-recycling-revenue.md (approved geofence-visit model). Brief: docs/plan-recycling-manual-revenue.md. KEY RISK: dedupe if a delayed geofence visit later appears for the same trip (merge by facility+date+truck, or manual link).</t>
         </is>
       </c>
     </row>

--- a/docs/CrewLogic-Future-Work-Register.xlsx
+++ b/docs/CrewLogic-Future-Work-Register.xlsx
@@ -527,7 +527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H54"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -543,7 +543,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CrewLogic Future-Work Register - stable IDs FW-01..FW-51 (do NOT renumber) - 2026-07-05  |  12 Done, 5 Partial, 3 Dropped, 31 Open  |  +FW-67 added 2026-08-16 (Recycling manual-revenue; note: FW-52..66 allocated outside this file)</t>
+          <t>CrewLogic Future-Work Register - stable IDs FW-01..FW-51 (do NOT renumber) - 2026-07-05  |  12 Done, 5 Partial, 3 Dropped, 31 Open  |  +FW-67 added 2026-08-16 (Recycling manual-revenue; note: FW-52..66 allocated outside this file)  |  +FW-68 (desktop UI) 2026-08-16</t>
         </is>
       </c>
     </row>
@@ -2562,6 +2562,44 @@
       <c r="H54" s="4" t="inlineStr">
         <is>
           <t>Extends docs/contract-recycling-revenue.md (approved geofence-visit model). Brief: docs/plan-recycling-manual-revenue.md. KEY RISK: dedupe if a delayed geofence visit later appears for the same trip (merge by facility+date+truck, or manual link).</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>FW-68</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>UI / UX</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>Professional desktop UI (responsive SaaS shell)</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>App is mobile-first/PWA; desktop landings get the narrow mobile UI, which looks unprofessional and wastes the screen. Owner wants desktop to render a standard SaaS layout (left expandable nav, center content, upper-right account/settings) like Motive/Linxup/CareerPlug/Google Cloud, while KEEPING the mobile UI for phones.</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>Backlog (owner 2026-08-16). RESPONSIVE split: a desktop app shell (left nav + top bar + center) wraps the EXISTING screens and drives hideAll()/show*/render* — additive chrome+nav, NOT a screen rewrite. Nav groups: Estimates, Dispatch, Business Development, Disaster Recovery, Other tools (price lookup/coupons/etc). Needs its own approved plan + HARD regression guard before code.</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="n"/>
+      <c r="G55" s="10" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>LARGE cross-cutting UI project on a 25k-line single file — mandatory code-gen regression-guard (preserve every screen/nav path; desktop shell is additive). Brief: docs/plan-desktop-ui-redesign.md. Open: breakpoint, hand-roll vs framework, Disaster Recovery scope, hash routing, one-file vs split.</t>
         </is>
       </c>
     </row>

--- a/docs/CrewLogic-Future-Work-Register.xlsx
+++ b/docs/CrewLogic-Future-Work-Register.xlsx
@@ -2588,7 +2588,7 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Backlog (owner 2026-08-16). RESPONSIVE split: a desktop app shell (left nav + top bar + center) wraps the EXISTING screens and drives hideAll()/show*/render* — additive chrome+nav, NOT a screen rewrite. Nav groups: Estimates, Dispatch, Business Development, Disaster Recovery, Other tools (price lookup/coupons/etc). Needs its own approved plan + HARD regression guard before code.</t>
+          <t>Backlog (owner 2026-08-16). RESPONSIVE split: a desktop app shell (left nav + top bar + center) wraps the EXISTING screens and drives hideAll()/show*/render* — additive chrome+nav, NOT a screen rewrite. Nav groups: Estimates, Dispatch, Business Development, Disaster Recovery, Other tools (price lookup/coupons/etc). Needs its own approved plan + HARD regression guard before code. Also redesign SETTINGS the same way: left category menu (Franchise, Account, Trucks, Cost, Proposal, Routes, Pricing, Yard Signs, Tools...) + right detail in columns/portlets (e.g. Franchise = Branding portlet + Company Info portlet) instead of the current top icon-links.</t>
         </is>
       </c>
       <c r="F55" s="4" t="n"/>
